--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.90/Food use (.1010)/Argentina.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.90/Food use (.1010)/Argentina.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.90\식품용(.1010)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.90\식품용(.1010)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2037,7 +2037,7 @@
         <v>47</v>
       </c>
       <c r="F7" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="F15" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
